--- a/data/trans_orig/P44-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44-Edad-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2012 (tasa de respuesta: 97,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -712,7 +712,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7481</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20509</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -835,107 +835,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>195</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>220416</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>211559</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267536</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256885</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>436</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>487952</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>473883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>498170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -948,114 +948,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234588</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234588</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288045</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288045</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>467</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522633</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522633</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>522633</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27501</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74212</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -1178,107 +1178,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>345</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>360876</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>386605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>370</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>406594</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>416508</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>781358</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>760263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>797143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -1291,114 +1291,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>379</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414106</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>414106</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441465</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441465</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441465</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>779</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855570</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855570</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>855570</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32735</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47165</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44737</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66121</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -1521,107 +1521,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267922</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>253492</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>277220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316707</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305356</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326658</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>554</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>584629</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>567040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -1634,114 +1634,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>273</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>340</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350093</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350093</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>350093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>613</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>650750</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>650750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>650750</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1751,37 +1751,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>27509</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7524</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>21295</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13078</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>44</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>48804</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24945</t>
+          <t>36263</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1864,107 +1864,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>220416</t>
+          <t>217189</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210986</t>
+          <t>205554</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227064</t>
+          <t>226824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>330</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>267536</t>
+          <t>366582</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256983</t>
+          <t>355175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>274967</t>
+          <t>374706</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>522</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>487952</t>
+          <t>583771</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474469</t>
+          <t>569059</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>497688</t>
+          <t>596312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -1977,22 +1977,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>234588</t>
+          <t>244698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>234588</t>
+          <t>244698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>234588</t>
+          <t>244698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2012,22 +2012,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>349</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>288045</t>
+          <t>387877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>288045</t>
+          <t>387877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>288045</t>
+          <t>387877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2047,22 +2047,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>467</t>
+          <t>566</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>522633</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>522633</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>522633</t>
+          <t>632575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>113757</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27838</t>
+          <t>91941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53999</t>
+          <t>138120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>110061</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>91432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49336</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>198</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74212</t>
+          <t>223818</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58183</t>
+          <t>196684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95019</t>
+          <t>256243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -2207,107 +2207,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>978</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>374765</t>
+          <t>1080292</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360107</t>
+          <t>1055929</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386268</t>
+          <t>1102108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>406594</t>
+          <t>1357419</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>392129</t>
+          <t>1333678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>417159</t>
+          <t>1376048</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>781358</t>
+          <t>2437710</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>760551</t>
+          <t>2405285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>797387</t>
+          <t>2464844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -2320,22 +2320,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>1194049</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>1194049</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>1194049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2355,22 +2355,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>441465</t>
+          <t>1467480</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>441465</t>
+          <t>1467480</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>441465</t>
+          <t>1467480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2390,22 +2390,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>855570</t>
+          <t>2661528</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>855570</t>
+          <t>2661528</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>855570</t>
+          <t>2661528</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,1054 +2425,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>32735</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>21457</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>47329</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>33386</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>23799</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>44678</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>66121</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>49989</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>83177</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>10,16%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>12,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>267922</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>253328</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>279200</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>89,11%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>84,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>316707</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>305415</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>326294</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>87,24%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>584629</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>567573</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>600761</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>89,84%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>87,22%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>300657</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>300657</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>300657</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>350093</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>350093</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>350093</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>650750</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>650750</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>650750</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27509</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>18443</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>39335</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11,24%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,07%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>21295</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>13322</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>32229</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>5,49%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>3,43%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>8,31%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>48804</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>35547</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>64903</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>217189</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>205363</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>226255</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>88,76%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>83,93%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>366582</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>355648</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>374555</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>94,51%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>91,69%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>96,57%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>522</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>583771</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>567672</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>597028</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>92,28%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>89,74%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>94,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>244698</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>244698</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>244698</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>387877</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>387877</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>387877</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>632575</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>632575</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>632575</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>113757</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>92764</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>138282</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>9,53%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>110061</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>89516</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>131398</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>223818</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>194216</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>254540</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1080292</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1055767</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1101285</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>90,47%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1357419</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1336082</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1377964</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2437710</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2406988</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2467312</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1194049</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1194049</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1194049</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1467480</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1467480</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1467480</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2425</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2661528</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2661528</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2661528</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3485,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3516,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,7 +2659,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -3701,107 +2669,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26782</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51399</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -3814,107 +2782,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>303498</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>291200</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>312444</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>309989</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>300099</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>613487</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>599907</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>624631</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -3927,114 +2895,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330280</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>330280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321026</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321026</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>321026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>651306</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>651306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>651306</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -4044,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52395</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>68271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37840</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90235</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72712</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>109877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -4157,107 +3125,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>378</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>425523</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>409647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>438771</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>459009</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>445392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>778</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>884532</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>864890</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>902055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -4270,114 +3238,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>424</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477918</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>477918</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>433</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496849</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496849</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496849</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>857</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>974767</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>974767</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>974767</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -4387,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58640</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78172</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62386</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>96753</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -4500,107 +3468,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>283</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>289398</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>344522</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>354341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>605</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>633920</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>615339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>649706</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,24%</t>
         </is>
       </c>
     </row>
@@ -4613,114 +3581,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334330</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>354</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>712092</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>712092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>712092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -4730,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26782</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>32013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>52554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11037</t>
+          <t>37182</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>25712</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>53208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>75</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>77942</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27319</t>
+          <t>60454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52325</t>
+          <t>96655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4843,107 +3811,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>303498</t>
+          <t>216239</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291473</t>
+          <t>204444</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313183</t>
+          <t>224985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>273</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>309989</t>
+          <t>362987</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301335</t>
+          <t>346961</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>315675</t>
+          <t>374457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>528</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>613487</t>
+          <t>579225</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>598981</t>
+          <t>560512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>623987</t>
+          <t>596713</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -4956,22 +3924,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>302</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>330280</t>
+          <t>256998</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>330280</t>
+          <t>256998</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>330280</t>
+          <t>256998</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4991,22 +3959,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>301</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>321026</t>
+          <t>400169</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>321026</t>
+          <t>400169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>321026</t>
+          <t>400169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5026,22 +3994,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>603</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>651306</t>
+          <t>657167</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>651306</t>
+          <t>657167</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>651306</t>
+          <t>657167</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5063,7 +4031,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -5073,107 +4041,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>164868</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39275</t>
+          <t>141503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68847</t>
+          <t>191432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>103</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37840</t>
+          <t>119300</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>99931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>145022</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>90235</t>
+          <t>284168</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73908</t>
+          <t>254479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110675</t>
+          <t>319383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -5186,107 +4154,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>425523</t>
+          <t>1234658</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409071</t>
+          <t>1208094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>438643</t>
+          <t>1258023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>459009</t>
+          <t>1476506</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>445038</t>
+          <t>1450784</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>470817</t>
+          <t>1495875</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>884532</t>
+          <t>2711164</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>864092</t>
+          <t>2675949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>900859</t>
+          <t>2740853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -5299,22 +4267,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>477918</t>
+          <t>1399526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>477918</t>
+          <t>1399526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>477918</t>
+          <t>1399526</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5334,22 +4302,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>496849</t>
+          <t>1595806</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>496849</t>
+          <t>1595806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>496849</t>
+          <t>1595806</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5369,22 +4337,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>974767</t>
+          <t>2995332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>974767</t>
+          <t>2995332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>974767</t>
+          <t>2995332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5404,1054 +4372,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>44932</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>32592</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>57500</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>13,44%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,2%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>33240</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>23191</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>46349</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>78172</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>62810</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>96210</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>289398</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>276830</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>301738</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>86,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>82,8%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>90,25%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>344522</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>331413</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>354571</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>633920</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>615882</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>649282</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>86,49%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>334330</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>334330</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>334330</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>377762</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>377762</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>377762</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>712092</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>712092</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>712092</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>40759</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>31051</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>52185</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>37182</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>25054</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>51193</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>9,29%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>77942</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>61784</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>97158</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>216239</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>204813</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>225947</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>84,14%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>79,69%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>87,92%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>362987</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>348976</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>375115</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>90,71%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>87,21%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>579225</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>560009</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>595383</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>85,22%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>90,6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>256998</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>256998</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>256998</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>400169</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>400169</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>400169</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>657167</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>657167</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>657167</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>164868</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>141704</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>191956</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>11,78%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>10,13%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>119300</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>98308</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>141896</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>284168</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>250835</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>316911</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>8,37%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>1234658</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1207570</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1257822</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>88,22%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>89,87%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1476506</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1453910</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1497498</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>92,52%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>93,84%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2711164</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>2678421</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2744497</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>90,51%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1399526</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1399526</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1399526</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>1387</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1595806</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1595806</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1595806</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2738</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2995332</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>2995332</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>2995332</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6464,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W28"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6495,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023</t>
+          <t>Población según si se han realizado alguna vez una prueba para detectar el Cáncer de colon en 2023 (tasa de respuesta: 98,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6670,7 +4606,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -6680,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333172</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149229</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>465467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72036</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>60311</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405209</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>632637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,24%</t>
         </is>
       </c>
     </row>
@@ -6793,107 +4729,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202470</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>70175</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>386413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>369</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>222126</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>233851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>424595</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>197167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>611205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,66%</t>
         </is>
       </c>
     </row>
@@ -6906,114 +4842,114 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535642</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>489</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294162</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294162</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>294162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>789</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>829804</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -7023,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>217</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>183248</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162700</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>202298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>281</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155949</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140680</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>171222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>498</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339197</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>365088</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -7136,107 +5072,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>357447</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>662</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358767</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>343494</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>374036</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>716214</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>743527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -7249,114 +5185,114 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>637</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>540695</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>943</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>514716</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>514716</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>514716</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1055411</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1055411</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1055411</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -7366,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164570</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148925</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>143059</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58451</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223849</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>539</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>307629</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -7479,107 +5415,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194026</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>209671</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>511</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>453216</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>372426</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>537824</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>816</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>647242</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>555411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>801666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -7592,114 +5528,114 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>555</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>800</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>596275</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954871</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954871</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>954871</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -7709,107 +5645,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>156</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>99507</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154465</t>
+          <t>87066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>466614</t>
+          <t>112345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>210</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>108379</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61626</t>
+          <t>96503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84402</t>
+          <t>121382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>366</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>207885</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219164</t>
+          <t>190902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>645615</t>
+          <t>227339</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -7822,107 +5758,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>290</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>202470</t>
+          <t>175584</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69028</t>
+          <t>162746</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>381177</t>
+          <t>188025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>626</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>222126</t>
+          <t>294430</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>209760</t>
+          <t>281427</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232536</t>
+          <t>306306</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>916</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>424595</t>
+          <t>470015</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184189</t>
+          <t>450561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>610640</t>
+          <t>486998</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>71,84%</t>
         </is>
       </c>
     </row>
@@ -7935,22 +5871,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>446</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>275091</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>275091</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>275091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7970,22 +5906,22 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>836</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>402809</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>402809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>402809</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8005,22 +5941,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>677900</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>677900</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>677900</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8042,7 +5978,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -8052,107 +5988,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>715</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>780497</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>161824</t>
+          <t>611744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203220</t>
+          <t>1112299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>900</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>479423</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139166</t>
+          <t>303346</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>170989</t>
+          <t>548100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>1259920</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>313632</t>
+          <t>1025251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367066</t>
+          <t>1748115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>49,69%</t>
         </is>
       </c>
     </row>
@@ -8165,107 +6101,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>357447</t>
+          <t>929527</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>337475</t>
+          <t>597725</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>378871</t>
+          <t>1098280</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>358767</t>
+          <t>1328539</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>343727</t>
+          <t>1259862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>375550</t>
+          <t>1504616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>716214</t>
+          <t>2258066</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>688345</t>
+          <t>1769871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>741779</t>
+          <t>2492735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -8278,22 +6214,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>1710024</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>1710024</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>1710024</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8313,22 +6249,22 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>3068</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>1807962</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>1807962</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>1807962</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8348,22 +6284,22 @@
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>3517986</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>3517986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>3517986</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8383,1054 +6319,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>164570</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>149887</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>181273</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>45,89%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>41,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>50,55%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>143059</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>47149</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>224205</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>23,99%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>37,6%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>307629</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>152290</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>398279</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>32,22%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>41,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>194026</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>177323</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>208709</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>54,11%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>453216</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>372070</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>549126</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>76,01%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>62,4%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>816</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>647242</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>556592</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>802581</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>67,78%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>58,29%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>358596</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>358596</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>358596</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>596275</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>596275</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>596275</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>954871</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>954871</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>954871</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>99507</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>86973</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>112999</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,62%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>108379</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>95410</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>120728</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>366</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>207885</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>188798</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>225101</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>175584</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>162092</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>188118</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>63,83%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>68,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>294430</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>282081</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>307399</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>73,09%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>70,03%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>470015</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>452799</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>489102</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>275091</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>275091</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>275091</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>402809</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>402809</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>402809</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>1282</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>677900</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>677900</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>677900</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>780497</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>613221</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1137669</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>35,86%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>66,53%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>479423</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>315898</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>550702</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>26,52%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>30,46%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1615</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1259920</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1034627</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1733043</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>35,81%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>29,41%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>49,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>929527</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>572355</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>1096803</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>64,14%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1328539</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1257260</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1492064</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>73,48%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>69,54%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3391</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>2258066</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1784943</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>2483359</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>64,19%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>50,74%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>70,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>1710024</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1710024</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1710024</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3068</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1807962</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>1807962</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>1807962</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>5006</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>3517986</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>3517986</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>3517986</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_orig/P44-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P44-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7481</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24570</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12980</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48750</t>
+          <t>48038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211559</t>
+          <t>210018</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>227107</t>
+          <t>226160</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256885</t>
+          <t>256548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275065</t>
+          <t>275173</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>473883</t>
+          <t>474595</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>498170</t>
+          <t>498462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53230</t>
+          <t>54537</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24957</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>47720</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58427</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95307</t>
+          <t>93562</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360876</t>
+          <t>359569</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>386605</t>
+          <t>386209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393311</t>
+          <t>393745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>416508</t>
+          <t>418235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>760263</t>
+          <t>762008</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>797143</t>
+          <t>797221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23437</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47165</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>45222</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51011</t>
+          <t>51438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83710</t>
+          <t>84549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253492</t>
+          <t>252467</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>277220</t>
+          <t>278855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>305356</t>
+          <t>304871</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>326671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>567040</t>
+          <t>566201</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>599739</t>
+          <t>599312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>18659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39144</t>
+          <t>39240</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>13068</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>31737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36263</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>64655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>205554</t>
+          <t>205458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226824</t>
+          <t>226039</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>355175</t>
+          <t>356140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374706</t>
+          <t>374809</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>569059</t>
+          <t>567920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596312</t>
+          <t>597102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>91941</t>
+          <t>92930</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133802</t>
+          <t>131805</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>196684</t>
+          <t>194689</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256243</t>
+          <t>257344</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1055929</t>
+          <t>1057096</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1102108</t>
+          <t>1101119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1333678</t>
+          <t>1335675</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1376048</t>
+          <t>1377246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2405285</t>
+          <t>2404184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2464844</t>
+          <t>2466839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>17958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39080</t>
+          <t>37644</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>20035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51399</t>
+          <t>51292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291200</t>
+          <t>292636</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>312444</t>
+          <t>312322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>300099</t>
+          <t>300991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315273</t>
+          <t>315020</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>599907</t>
+          <t>600014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624631</t>
+          <t>625132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39147</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68271</t>
+          <t>69271</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26743</t>
+          <t>26431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51457</t>
+          <t>51413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72712</t>
+          <t>73402</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109877</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>409647</t>
+          <t>408647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438771</t>
+          <t>437984</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445392</t>
+          <t>445436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470106</t>
+          <t>470418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>864890</t>
+          <t>864147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>902055</t>
+          <t>901365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58640</t>
+          <t>58905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46019</t>
+          <t>45699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62386</t>
+          <t>63518</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96753</t>
+          <t>97713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275690</t>
+          <t>275425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>301439</t>
+          <t>301520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331743</t>
+          <t>332063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>354341</t>
+          <t>354900</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615339</t>
+          <t>614379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649706</t>
+          <t>648574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>32013</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52554</t>
+          <t>52158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>50864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60454</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96655</t>
+          <t>96242</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204444</t>
+          <t>204840</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224985</t>
+          <t>226159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>346961</t>
+          <t>349305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374457</t>
+          <t>375285</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>560512</t>
+          <t>560925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>596713</t>
+          <t>593885</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141503</t>
+          <t>140424</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191432</t>
+          <t>189496</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99931</t>
+          <t>98230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145022</t>
+          <t>143470</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>254479</t>
+          <t>253370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>319383</t>
+          <t>322040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1208094</t>
+          <t>1210030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1258023</t>
+          <t>1259102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1450784</t>
+          <t>1452336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1495875</t>
+          <t>1497576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2675949</t>
+          <t>2673292</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2740853</t>
+          <t>2741962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>333172</t>
+          <t>94995</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>149229</t>
+          <t>79322</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>465467</t>
+          <t>112613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60311</t>
+          <t>64599</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83253</t>
+          <t>88353</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>405209</t>
+          <t>172255</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218599</t>
+          <t>151777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>632637</t>
+          <t>190196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>202470</t>
+          <t>214913</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70175</t>
+          <t>197295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386413</t>
+          <t>230586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>222126</t>
+          <t>235055</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>210909</t>
+          <t>223962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233851</t>
+          <t>247716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>424595</t>
+          <t>449967</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>197167</t>
+          <t>432026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611205</t>
+          <t>470445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>309908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>309908</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>535642</t>
+          <t>309908</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>312315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>312315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>294162</t>
+          <t>312315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>622222</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>622222</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>829804</t>
+          <t>622222</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,32 +4964,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162700</t>
+          <t>172913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>202298</t>
+          <t>215499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4999,32 +4999,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>155949</t>
+          <t>175138</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140680</t>
+          <t>158041</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171222</t>
+          <t>194126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>368708</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>311884</t>
+          <t>342377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>365088</t>
+          <t>395627</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>357447</t>
+          <t>392421</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338397</t>
+          <t>370492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377995</t>
+          <t>413078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>358767</t>
+          <t>399810</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343494</t>
+          <t>380822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>374036</t>
+          <t>416907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>716214</t>
+          <t>792231</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690323</t>
+          <t>765312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>743527</t>
+          <t>818562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,51%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>585991</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>585991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>540695</t>
+          <t>585991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>574948</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>574948</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514716</t>
+          <t>574948</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>1160939</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>1160939</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1055411</t>
+          <t>1160939</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>164570</t>
+          <t>178413</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148925</t>
+          <t>161551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179375</t>
+          <t>195086</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>143059</t>
+          <t>157555</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58451</t>
+          <t>141924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223849</t>
+          <t>172354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>307629</t>
+          <t>335968</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>153205</t>
+          <t>314405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399460</t>
+          <t>360306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>194026</t>
+          <t>217654</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179221</t>
+          <t>200981</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>209671</t>
+          <t>234516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>453216</t>
+          <t>267151</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372426</t>
+          <t>252352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>537824</t>
+          <t>282782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>647242</t>
+          <t>484804</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555411</t>
+          <t>460466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>801666</t>
+          <t>506367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>396067</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>396067</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>396067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>596275</t>
+          <t>424706</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>596275</t>
+          <t>424706</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>596275</t>
+          <t>424706</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>954871</t>
+          <t>820772</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>954871</t>
+          <t>820772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>954871</t>
+          <t>820772</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>99507</t>
+          <t>108487</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87066</t>
+          <t>94181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>112345</t>
+          <t>122515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>108379</t>
+          <t>120049</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96503</t>
+          <t>106645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121382</t>
+          <t>133772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>207885</t>
+          <t>228535</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>190902</t>
+          <t>208685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227339</t>
+          <t>247962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>175584</t>
+          <t>193522</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162746</t>
+          <t>179494</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188025</t>
+          <t>207828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>294430</t>
+          <t>319472</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281427</t>
+          <t>305749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>306306</t>
+          <t>332876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>470015</t>
+          <t>512994</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>450561</t>
+          <t>493567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>486998</t>
+          <t>532844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275091</t>
+          <t>302009</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275091</t>
+          <t>302009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275091</t>
+          <t>302009</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>402809</t>
+          <t>439521</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>402809</t>
+          <t>439521</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>402809</t>
+          <t>439521</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>677900</t>
+          <t>741529</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>677900</t>
+          <t>741529</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>677900</t>
+          <t>741529</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>780497</t>
+          <t>575464</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>611744</t>
+          <t>540928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1112299</t>
+          <t>611536</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>479423</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303346</t>
+          <t>501033</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>548100</t>
+          <t>558655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1259920</t>
+          <t>1105467</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1025251</t>
+          <t>1057958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1748115</t>
+          <t>1152250</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>929527</t>
+          <t>1018510</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>597725</t>
+          <t>982438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1098280</t>
+          <t>1053046</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>63,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1328539</t>
+          <t>1221487</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1259862</t>
+          <t>1192834</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1504616</t>
+          <t>1250456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>71,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2258066</t>
+          <t>2239996</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1769871</t>
+          <t>2193213</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2492735</t>
+          <t>2287505</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1710024</t>
+          <t>1593974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1807962</t>
+          <t>1751489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3517986</t>
+          <t>3345463</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
